--- a/Project_Up/history.xlsx
+++ b/Project_Up/history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,92 +417,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Price (₹)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Mkt Cap (Cr)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Above 200 EMA%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Vol Ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Prior Uptrend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>3D Squeeze</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Net Accum</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Rising Lows</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Entry Trigger</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Score /10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Buy Zone</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Target (₹)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Stop (₹)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>

--- a/Project_Up/history.xlsx
+++ b/Project_Up/history.xlsx
@@ -35,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,11 +50,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFF6FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,16 +97,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -495,7 +487,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
@@ -620,7 +612,7 @@
           <t>13299</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
@@ -655,7 +647,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -687,92 +679,92 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>AJAXENGG</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Ajax Engineering Limited</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>579.1</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>6534</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>₹576.2–582.0</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>619.64</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>555.24</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:AJAXENGG</t>
         </is>
@@ -804,7 +796,7 @@
           <t>1092</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -839,7 +831,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -871,92 +863,92 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>METROPOLIS</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Metropolis Healthcare Limited</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>576.9</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>12204</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>₹574.02–579.78</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>606.0</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>533.66</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:METROPOLIS</t>
         </is>
@@ -988,7 +980,7 @@
           <t>393805</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
@@ -1023,7 +1015,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1055,92 +1047,92 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Adani Enterprises Limited</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>3168.5</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>428927</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>₹3152.66–3184.34</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>3228.78</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>2932.88</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
@@ -1172,7 +1164,7 @@
           <t>14350</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -1207,7 +1199,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1239,92 +1231,92 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SUDARSCHEM</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Sudarshan Chemical Industries Limited</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1252.8</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>10006</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>₹1246.54–1259.06</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>1340.5</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>1173.15</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM</t>
         </is>
@@ -1356,7 +1348,7 @@
           <t>28399</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
@@ -1391,7 +1383,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1423,92 +1415,92 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>TIINDIA</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Tube Investments Of India Limited</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>2870.0</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>54975</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>₹2855.65–2884.35</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>3070.9</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>2807.24</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:TIINDIA</t>
         </is>
@@ -1540,7 +1532,7 @@
           <t>96167</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
@@ -1575,7 +1567,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1607,92 +1599,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>JINDALPOLY</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Jindal Poly Films Limited</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>637.55</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>2784</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>₹634.36–640.74</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>682.18</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>625.78</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALPOLY</t>
         </is>
@@ -1724,7 +1716,7 @@
           <t>3171</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -1759,7 +1751,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1791,92 +1783,92 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>NUVAMA</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1805.0</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>33251</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>₹1795.97–1814.02</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>1931.35</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>1705.67</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:NUVAMA</t>
         </is>
@@ -1908,7 +1900,7 @@
           <t>1447</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
@@ -1943,7 +1935,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1975,92 +1967,92 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ASAHIINDIA</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Asahi India Glass Limited</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>951.25</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>24287</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>₹946.49–956.01</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>1017.84</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>927.09</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:ASAHIINDIA</t>
         </is>
@@ -2092,7 +2084,7 @@
           <t>458670</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
@@ -2127,7 +2119,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2159,92 +2151,92 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>APCOTEXIND</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Apcotex Industries Limited</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>625.25</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>3242</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>₹622.12–628.38</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>669.02</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>601.92</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:APCOTEXIND</t>
         </is>
@@ -2276,7 +2268,7 @@
           <t>223145</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -2311,7 +2303,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2343,92 +2335,92 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>TBZ</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>301.7</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>52.2</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>₹300.19–303.21</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>311.14</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>267.1</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:TBZ</t>
         </is>
@@ -2442,179 +2434,179 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fine Organic Industries Limited</t>
+          <t>Ethos Limited</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5272.7</t>
+          <t>2898.8</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>11.6</t>
+          <t>7693</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10.3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>₹5246.34–5299.06</t>
+          <t>2884.31-2913.29</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5367.83</t>
+          <t>3101.72</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5048.9</t>
+          <t>2821.2</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FINEORG</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>AURUM</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Aurum Proptech Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>233.5</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>₹232.33–234.67</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>249.85</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>223.99</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AURUM</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>KAMDHENU</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Kamdhenu Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>35.58</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>35.4-35.76</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>36.87</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>33.66</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KAMDHENU</t>
         </is>
       </c>
     </row>
@@ -2626,179 +2618,179 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Power Mech Projects Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2539.3</t>
+          <t>1162.9</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>2.6</t>
+          <t>118803</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>₹2526.6–2552.0</t>
+          <t>1157.09-1168.71</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2717.05</t>
+          <t>1198.97</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2463.12</t>
+          <t>1081.67</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POWERMECH</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>TATACAP</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Tata Capital Limited</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>370.55</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>158421</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>₹368.7–372.4</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>388.25</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>356.89</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TATACAP</t>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>48835.0</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>143469</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>48590.82-49079.17</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>48944.05</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>47312.1</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
         </is>
       </c>
     </row>
@@ -2810,179 +2802,179 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nuvama Wealth Management Limited</t>
+          <t>Ceigall India Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1787.9</t>
+          <t>341.25</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>16.1</t>
+          <t>5940</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11.0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>₹1778.96–1796.84</t>
+          <t>339.54-342.96</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1913.05</t>
+          <t>365.14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1705.67</t>
+          <t>318.33</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NUVAMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CEIGALL</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>EMUDHRA</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Emudhra Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>552.7</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>₹549.94–555.46</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>591.39</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>534.45</t>
-        </is>
-      </c>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA</t>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Limited</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>8693.5</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>43702</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>8650.03-8736.97</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>8731.62</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>8009.1</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NAVINFLUOR</t>
         </is>
       </c>
     </row>
@@ -2994,179 +2986,179 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Ethos Limited</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2895.7</t>
+          <t>1907.7</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>10.2</t>
+          <t>39241</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>₹2881.22–2910.18</t>
+          <t>1898.16-1917.24</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3098.4</t>
+          <t>2041.24</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2821.2</t>
+          <t>1841.5</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NH</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>HYUNDAI</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Hyundai Motor India Limited</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>2258.0</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>184203</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>1036.95</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>62539</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>₹2246.71–2269.29</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>2416.06</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>2168.1</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>1031.77-1042.13</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>1082.87</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>982.08</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTILALOFS</t>
         </is>
       </c>
     </row>
@@ -3178,179 +3170,179 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fedbank Financial Services Limited</t>
+          <t>Ipca Laboratories Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>159.82</t>
+          <t>1978.1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>7.0</t>
+          <t>49480</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>₹159.02–160.62</t>
+          <t>1968.21-1987.99</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>171.01</t>
+          <t>1982.04</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>153.3</t>
+          <t>1892.48</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FEDFINA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IPCALAB</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>GANDHITUBE</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Gandhi Special Tubes Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>902.0</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>AURUM</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Aurum Proptech Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>232.22</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>₹897.49–906.51</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>965.14</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>866.84</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GANDHITUBE</t>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>231.06-233.38</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>248.48</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>223.99</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AURUM</t>
         </is>
       </c>
     </row>
@@ -3362,179 +3354,179 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life Amc Limited</t>
+          <t>Anupam Rasayan India Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1023.8</t>
+          <t>1260.1</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>9.1</t>
+          <t>14350</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>₹1018.68–1028.92</t>
+          <t>1253.8-1266.4</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1095.47</t>
+          <t>1348.31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>982.67</t>
+          <t>1231.07</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ABSLAMC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ANURAS</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Fsn E-Commerce Ventures Limited</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>342.25</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>96167</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Titan Company Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>5130.9</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>458670</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>₹340.54–343.96</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>346.26</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>324.72</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>5105.25-5156.55</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>5160.77</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>5002.17</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
@@ -3546,179 +3538,179 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical Industries Limited</t>
+          <t>Emudhra Limited</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1257.1</t>
+          <t>549.25</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>22.4</t>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4.7</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>₹1250.81–1263.39</t>
+          <t>546.5-552.0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1345.1</t>
+          <t>587.7</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1205.42</t>
+          <t>534.45</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>SOLARINDS</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Solar Industries India Limited</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>20324.0</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>184600</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>GRPLTD</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Grp Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>1987.1</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>₹20222.38–20425.62</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>20568.64</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>19468.35</t>
-        </is>
-      </c>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>1977.16-1997.04</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>2126.2</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>1938.62</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRPLTD</t>
         </is>
       </c>
     </row>
@@ -3730,179 +3722,179 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Aurobindo Pharma Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1163.2</t>
+          <t>1684.4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>118803</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>13.5</t>
+          <t>94667</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>₹1157.38–1169.02</t>
+          <t>1675.98-1692.82</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1198.97</t>
+          <t>1694.48</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1081.67</t>
+          <t>1582.81</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>CEIGALL</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Ceigall India Limited</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>338.7</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>5940</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>₹337.01–340.39</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>362.41</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>318.33</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CEIGALL</t>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>11991.0</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>327291</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>11931.05-12050.95</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>11979.8</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>11501.82</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
@@ -3914,179 +3906,179 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Limited</t>
+          <t>Aditya Birla Sun Life Amc Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8650.0</t>
+          <t>1052.5</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43702</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>27.9</t>
+          <t>30322</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>12.1</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>₹8606.75–8693.25</t>
+          <t>1047.24-1057.76</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8731.62</t>
+          <t>1126.17</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8009.1</t>
+          <t>982.67</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NAVINFLUOR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>JSWDULUX</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Jsw Dulux Limited</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>3131.3</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>14167</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>₹3115.64–3146.96</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>3350.49</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>3036.03</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JSWDULUX</t>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>413.45</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>302040</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>411.38-415.52</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>442.39</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>401.89</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BEL</t>
         </is>
       </c>
     </row>
@@ -4098,179 +4090,179 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SANDHAR</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sandhar Technologies Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>665.0</t>
+          <t>1928.5</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>15.1</t>
+          <t>460672</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>7.0</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>₹661.67–668.32</t>
+          <t>1918.86-1938.14</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>711.55</t>
+          <t>2036.67</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>635.78</t>
+          <t>1877.24</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SANDHAR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>KAMDHENU</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Kamdhenu Limited</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>₹35.72–36.08</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>36.87</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:KAMDHENU</t>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>1265.7</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>393805</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>1259.37-1272.03</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>1354.3</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>1217.5</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
         </is>
       </c>
     </row>

--- a/Project_Up/history.xlsx
+++ b/Project_Up/history.xlsx
@@ -35,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,13 +102,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +495,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
@@ -612,7 +620,7 @@
           <t>13299</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
@@ -647,7 +655,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -679,92 +687,92 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>AJAXENGG</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Ajax Engineering Limited</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>579.1</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>6534</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>₹576.2–582.0</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>619.64</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>555.24</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:AJAXENGG</t>
         </is>
@@ -796,7 +804,7 @@
           <t>1092</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -831,7 +839,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -863,92 +871,92 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>METROPOLIS</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Metropolis Healthcare Limited</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>576.9</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>12204</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>₹574.02–579.78</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>606.0</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>533.66</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:METROPOLIS</t>
         </is>
@@ -980,7 +988,7 @@
           <t>393805</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
@@ -1015,7 +1023,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1047,92 +1055,92 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Adani Enterprises Limited</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>3168.5</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>428927</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>₹3152.66–3184.34</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>3228.78</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>2932.88</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIENT</t>
         </is>
@@ -1164,7 +1172,7 @@
           <t>14350</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -1199,7 +1207,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1231,92 +1239,92 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>SUDARSCHEM</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Sudarshan Chemical Industries Limited</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>1252.8</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>10006</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>₹1246.54–1259.06</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>1340.5</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>1173.15</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM</t>
         </is>
@@ -1348,7 +1356,7 @@
           <t>28399</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
@@ -1383,7 +1391,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1415,92 +1423,92 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>TIINDIA</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Tube Investments Of India Limited</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>2870.0</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>54975</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>₹2855.65–2884.35</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>3070.9</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>2807.24</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:TIINDIA</t>
         </is>
@@ -1532,7 +1540,7 @@
           <t>96167</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
@@ -1567,7 +1575,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1599,92 +1607,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>JINDALPOLY</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Jindal Poly Films Limited</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>637.55</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2784</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>₹634.36–640.74</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>682.18</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>625.78</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALPOLY</t>
         </is>
@@ -1716,7 +1724,7 @@
           <t>3171</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -1751,7 +1759,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1783,92 +1791,92 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>NUVAMA</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>1805.0</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>33251</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>₹1795.97–1814.02</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>1931.35</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>1705.67</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:NUVAMA</t>
         </is>
@@ -1900,7 +1908,7 @@
           <t>1447</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
@@ -1935,7 +1943,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1967,92 +1975,92 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>ASAHIINDIA</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Asahi India Glass Limited</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>951.25</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>24287</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>₹946.49–956.01</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>1017.84</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>927.09</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:ASAHIINDIA</t>
         </is>
@@ -2084,7 +2092,7 @@
           <t>458670</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
@@ -2119,7 +2127,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2151,92 +2159,92 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>APCOTEXIND</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Apcotex Industries Limited</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>625.25</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>3242</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>₹622.12–628.38</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>669.02</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>601.92</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:APCOTEXIND</t>
         </is>
@@ -2268,7 +2276,7 @@
           <t>223145</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -2303,7 +2311,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2335,92 +2343,92 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>TBZ</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>301.7</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>52.2</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>₹300.19–303.21</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>311.14</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>267.1</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>https://www.tradingview.com/chart/?symbol=NSE:TBZ</t>
         </is>
@@ -2444,7 +2452,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2898.8</t>
+          <t>2898.7</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2452,54 +2460,54 @@
           <t>7693</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2884.31-2913.29</t>
+          <t>₹2884.21–2913.19</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3101.72</t>
+          <t>3101.61</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2519,94 +2527,94 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>KAMDHENU</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Kamdhenu Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>35.58</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>25.9</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>CEIGALL</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Ceigall India Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>341.35</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>5940</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>35.4-35.76</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>36.87</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:KAMDHENU</t>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>₹339.64–343.06</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>365.24</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>318.33</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CEIGALL</t>
         </is>
       </c>
     </row>
@@ -2618,27 +2626,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Navin Fluorine International Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1162.9</t>
+          <t>8675.5</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118803</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13.5</t>
+          <t>43702</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2648,149 +2656,149 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1157.09-1168.71</t>
+          <t>₹8632.12–8718.88</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1198.97</t>
+          <t>8731.62</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1081.67</t>
+          <t>8009.1</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NAVINFLUOR</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Bosch Limited</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>48835.0</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>143469</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>1042.9</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>62539</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>48590.82-49079.17</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>48944.05</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>47312.1</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>₹1037.69–1048.11</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>1082.87</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>982.08</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTILALOFS</t>
         </is>
       </c>
     </row>
@@ -2802,179 +2810,179 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ceigall India Limited</t>
+          <t>Ipca Laboratories Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>341.25</t>
+          <t>1974.9</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11.0</t>
+          <t>49480</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>24.4</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>339.54-342.96</t>
+          <t>₹1965.03–1984.77</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>365.14</t>
+          <t>1982.04</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>318.33</t>
+          <t>1892.48</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CEIGALL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IPCALAB</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>NAVINFLUOR</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Navin Fluorine International Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>8693.5</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>43702</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>28.6</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Emudhra Limited</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>547.85</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>8650.03-8736.97</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>8731.62</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>8009.1</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NAVINFLUOR</t>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>₹545.11–550.59</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>586.2</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>534.45</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA</t>
         </is>
       </c>
     </row>
@@ -2986,179 +2994,179 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>Iris Clothings Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1907.7</t>
+          <t>58.48</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>44.6</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1898.16-1917.24</t>
+          <t>₹58.19–58.77</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2041.24</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1841.5</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NH</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IRISDOREME</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Motilal Oswal Financial Services Limited</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>1036.95</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>62539</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>1031.77-1042.13</t>
-        </is>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>1082.87</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>982.08</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="R29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTILALOFS</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Axiscades Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>1671.2</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>₹1662.84–1679.56</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>1788.18</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>1542.22</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISCADES</t>
         </is>
       </c>
     </row>
@@ -3170,179 +3178,179 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Limited</t>
+          <t>Torrent Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1978.1</t>
+          <t>5066.0</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49480</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>24.6</t>
+          <t>192086</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>16.7</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1968.21-1987.99</t>
+          <t>₹5040.67–5091.33</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1982.04</t>
+          <t>5223.75</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1892.48</t>
+          <t>4806.94</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IPCALAB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>AURUM</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Aurum Proptech Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>232.22</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>231.06-233.38</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>248.48</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>223.99</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AURUM</t>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>ABSLAMC</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Aditya Birla Sun Life Amc Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1051.8</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>30322</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>₹1046.54–1057.06</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>1125.43</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>982.67</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ABSLAMC</t>
         </is>
       </c>
     </row>
@@ -3354,179 +3362,179 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Limited</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1260.1</t>
+          <t>898.75</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1.6</t>
+          <t>118856</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1253.8-1266.4</t>
+          <t>₹894.26–903.24</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1348.31</t>
+          <t>961.66</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1231.07</t>
+          <t>856.15</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ANURAS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIANB</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Titan Company Limited</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>5130.9</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>458670</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>5105.25-5156.55</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>5160.77</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>5002.17</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>393805</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>₹1293.5–1306.5</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>1391.0</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>1217.5</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
         </is>
       </c>
     </row>
@@ -3538,179 +3546,179 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Emudhra Limited</t>
+          <t>Bharat Electronics Limited</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>549.25</t>
+          <t>414.45</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>4.7</t>
+          <t>302040</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>546.5-552.0</t>
+          <t>₹412.38–416.52</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>587.7</t>
+          <t>443.46</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>534.45</t>
+          <t>401.89</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BEL</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>GRPLTD</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Grp Limited</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>1987.1</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>1977.16-1997.04</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>2126.2</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>1938.62</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GRPLTD</t>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Bosch Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>143469</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>₹49750.0–50250.0</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>49750.0</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>47312.1</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
         </is>
       </c>
     </row>
@@ -3722,179 +3730,179 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1684.4</t>
+          <t>388.8</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>94667</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>21.9</t>
+          <t>102534</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1675.98-1692.82</t>
+          <t>₹386.86–390.74</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1694.48</t>
+          <t>416.02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1582.81</t>
+          <t>370.51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Bajaj Auto Limited</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>11991.0</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>327291</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>FINEORG</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Fine Organic Industries Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>5282.8</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>16196</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>11931.05-12050.95</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>11979.8</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>11501.82</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>₹5256.39–5309.21</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>5367.83</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>5048.9</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:FINEORG</t>
         </is>
       </c>
     </row>
@@ -3906,179 +3914,179 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life Amc Limited</t>
+          <t>Dlf Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1052.5</t>
+          <t>691.05</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>12.1</t>
+          <t>168272</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1047.24-1057.76</t>
+          <t>₹687.59–694.51</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1126.17</t>
+          <t>739.42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>982.67</t>
+          <t>657.36</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ABSLAMC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Bharat Electronics Limited</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>413.45</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>302040</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ARFIN</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Arfin India Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>87.23</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>411.38-415.52</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>442.39</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>401.89</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BEL</t>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>₹86.79–87.67</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>93.34</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>82.77</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ARFIN</t>
         </is>
       </c>
     </row>
@@ -4090,179 +4098,179 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>GANDHITUBE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Limited</t>
+          <t>Gandhi Special Tubes Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1928.5</t>
+          <t>900.95</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>460672</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>7.0</t>
+          <t>1092</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1918.86-1938.14</t>
+          <t>₹896.45–905.45</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2036.67</t>
+          <t>964.02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1877.24</t>
+          <t>866.84</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GANDHITUBE</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Axis Bank Limited</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>1265.7</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>393805</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Sbc Exports Limited</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>42.15</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>1259.37-1272.03</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>1354.3</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>1217.5</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AXISBANK</t>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>₹41.94–42.36</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>44.77</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>39.31</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SBC</t>
         </is>
       </c>
     </row>

--- a/Project_Up/history.xlsx
+++ b/Project_Up/history.xlsx
@@ -11,7 +11,8 @@
     <sheet name="2026-09-03" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-09-04" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-09-07" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="History" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-09-08" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="History" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7045,6 +7046,1431 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Price (₹)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mkt Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Above 200 EMA%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Vol Ratio</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Prior Uptrend</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>3D Squeeze</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Net Accum</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rising Lows</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Entry Trigger</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Score /10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Zone</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Target (₹)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Stop (₹)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>R:R</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GUFICBIO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Gufic Biosciences Limited</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>448.9</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>446.66-451.14</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>451.68</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>410.45</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GUFICBIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>AGARWALEYE</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Agarwal'S Health Care Limited</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>519.2</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>16296</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>516.6-521.8</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>555.54</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>500.84</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AGARWALEYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>The Great Eastern Shipping Company Limited</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1379.2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19537</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1372.3-1386.1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1475.74</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1289.97</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GESHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SKIPPER</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Skipper Limited</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>604.1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>601.08-607.12</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>613.61</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>518.72</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SKIPPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>127.05</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>126.41-127.69</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>135.94</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>119.31</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BLUSPRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1444.4</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>21625</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>1437.18-1451.62</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>1482.25</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>1368.67</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CHENNPETRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Krishival Foods Limited</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>417.5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>415.41-419.59</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>446.73</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>403.87</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KRISHIVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Lt Foods Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>461.2</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>458.89-463.51</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>488.25</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>425.25</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LTFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Limited</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8731.0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43907</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8687.34-8774.65</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8731.62</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>8192.75</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NAVINFLUOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOCLCORP</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Gocl Corporation Limited</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>438.4</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>436.21-440.59</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>457.6</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>378.72</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GOCLCORP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>KPIL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Kalpataru Projects International Limited</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1398.2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24021</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1391.21-1405.19</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1460.66</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1377.09</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KPIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Aster Dm Quality Care Limited</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>787.4</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>68492</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>783.46-791.34</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>842.52</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>737.6</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASTERDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SFL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Sheela Foam Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>681.75</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7479</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>678.34-685.16</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>729.47</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>626.17</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>IIFLCAPS</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Iifl Capital Services Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>341.6</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>10754</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>339.89-343.31</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>365.51</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>331.15</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IIFLCAPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>VIDHIING</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Vidhi Specialty Food Ingredients Limited</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>357.85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>356.06-359.64</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>382.9</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>331.75</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:VIDHIING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
